--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -1,80 +1,423 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\minigame\Assets\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3825A2DA-81DC-4703-8673-1BA1D39CC2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21920" yWindow="1680" windowWidth="15920" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="10600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
   <si>
     <t>GameCharacter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+  </si>
+  <si>
+    <t>炒番茄</t>
+  </si>
+  <si>
+    <t>炒鸡蛋</t>
   </si>
   <si>
     <t>番茄炒蛋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -82,24 +425,314 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -148,7 +781,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -183,7 +816,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -357,49 +990,88 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="11.875" customWidth="1"/>
     <col min="3" max="3" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
+      <c r="C2" s="2">
+        <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="C2">
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
         <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10600"/>
+    <workbookView windowWidth="13070" windowHeight="4410"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>ID</t>
+    <t>DishID</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,14 +63,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,155 +519,155 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -1,26 +1,6 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D84F397-A9E4-4838-8E72-6C9E45166BC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13070" windowHeight="4410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-</workbook>
-</file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>DishID</t>
   </si>
@@ -47,6 +27,40 @@
   </si>
   <si>
     <t>IconPath</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛肉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卷心菜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡腿</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤鱼</t>
+  </si>
+  <si>
+    <t>土豆咖喱牛腩</t>
+  </si>
+  <si>
+    <t>葱鸡腿</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -100,11 +114,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -376,104 +392,4 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2">
-        <v>101</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2">
-        <v>102</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>201</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2">
-        <v>202</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2">
-        <v>203</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
 </file>
--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -1,6 +1,27 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{797354A7-3577-4EE8-875D-1FDF101F0560}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="6230" yWindow="350" windowWidth="14400" windowHeight="8180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+</workbook>
+</file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>DishID</t>
   </si>
@@ -26,49 +47,38 @@
     <t>番茄炒蛋</t>
   </si>
   <si>
+    <t>烤鱼</t>
+  </si>
+  <si>
+    <t>土豆咖喱牛腩</t>
+  </si>
+  <si>
     <t>IconPath</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>牛肉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>卷心菜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>鸡腿</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>土豆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>番茄</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>烤鱼</t>
-  </si>
-  <si>
-    <t>土豆咖喱牛腩</t>
   </si>
   <si>
     <t>葱鸡腿</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,17 +87,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -112,13 +113,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -392,4 +389,228 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0000-0000-0000-000000000000}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="4" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1">
+        <v>101</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
+        <v>102</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>201</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1">
+        <v>202</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
+        <v>203</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1">
+        <v>103</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>104</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1">
+        <v>105</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1">
+        <v>106</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1">
+        <v>107</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <v>108</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <v>204</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1">
+        <v>205</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1">
+        <v>206</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{797354A7-3577-4EE8-875D-1FDF101F0560}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EDADB5-6E95-463B-86D2-32633EBC138A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6230" yWindow="350" windowWidth="14400" windowHeight="8180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>DishID</t>
   </si>
@@ -72,6 +71,33 @@
   </si>
   <si>
     <t>葱鸡腿</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/meat_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/cabage_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/chicken_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/potato_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/tomato_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/fish_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/fishdish_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/beafsoup_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/Onionchicken_icon.png</t>
   </si>
 </sst>
 </file>
@@ -392,7 +418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0000-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
@@ -493,8 +519,8 @@
       <c r="C7" s="1">
         <v>103</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -507,8 +533,8 @@
       <c r="C8" s="1">
         <v>104</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -521,8 +547,8 @@
       <c r="C9" s="1">
         <v>105</v>
       </c>
-      <c r="D9" s="1">
-        <v>0</v>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -535,8 +561,8 @@
       <c r="C10" s="1">
         <v>106</v>
       </c>
-      <c r="D10" s="1">
-        <v>0</v>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -549,8 +575,8 @@
       <c r="C11" s="1">
         <v>107</v>
       </c>
-      <c r="D11" s="1">
-        <v>0</v>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -563,8 +589,8 @@
       <c r="C12" s="1">
         <v>108</v>
       </c>
-      <c r="D12" s="1">
-        <v>0</v>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -577,8 +603,8 @@
       <c r="C13" s="1">
         <v>204</v>
       </c>
-      <c r="D13" s="1">
-        <v>0</v>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -591,8 +617,8 @@
       <c r="C14" s="1">
         <v>205</v>
       </c>
-      <c r="D14" s="1">
-        <v>0</v>
+      <c r="D14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -605,8 +631,8 @@
       <c r="C15" s="1">
         <v>206</v>
       </c>
-      <c r="D15" s="1">
-        <v>0</v>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -1,27 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{797354A7-3577-4EE8-875D-1FDF101F0560}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6230" yWindow="350" windowWidth="14400" windowHeight="8180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="10600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>DishID</t>
   </si>
@@ -32,6 +38,12 @@
     <t>GameCharacter</t>
   </si>
   <si>
+    <t>IconPath</t>
+  </si>
+  <si>
+    <t>OnEatBuffList</t>
+  </si>
+  <si>
     <t>番茄</t>
   </si>
   <si>
@@ -47,38 +59,50 @@
     <t>番茄炒蛋</t>
   </si>
   <si>
+    <t>牛肉</t>
+  </si>
+  <si>
+    <t>卷心菜</t>
+  </si>
+  <si>
+    <t>鸡腿</t>
+  </si>
+  <si>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>鱼</t>
+  </si>
+  <si>
     <t>烤鱼</t>
   </si>
   <si>
+    <t>13001;2|14001;5</t>
+  </si>
+  <si>
     <t>土豆咖喱牛腩</t>
   </si>
   <si>
-    <t>IconPath</t>
-  </si>
-  <si>
-    <t>牛肉</t>
-  </si>
-  <si>
-    <t>卷心菜</t>
-  </si>
-  <si>
-    <t>鸡腿</t>
-  </si>
-  <si>
-    <t>土豆</t>
-  </si>
-  <si>
-    <t>鱼</t>
+    <t>13001;0.5|14001;5</t>
   </si>
   <si>
     <t>葱鸡腿</t>
+  </si>
+  <si>
+    <t>13001;1|14001;5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,21 +111,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -109,9 +457,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -119,17 +709,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -387,19 +1021,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0000-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="8.6640625" style="1"/>
+    <col min="1" max="4" width="8.66666666666667" style="1"/>
+    <col min="5" max="5" width="37.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -410,15 +1045,18 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1">
         <v>101</v>
@@ -426,13 +1064,16 @@
       <c r="D2" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
         <v>102</v>
@@ -440,13 +1081,16 @@
       <c r="D3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1">
         <v>201</v>
@@ -454,13 +1098,16 @@
       <c r="D4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1">
         <v>202</v>
@@ -468,13 +1115,16 @@
       <c r="D5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1">
         <v>203</v>
@@ -482,13 +1132,16 @@
       <c r="D6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>103</v>
@@ -496,13 +1149,16 @@
       <c r="D7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
         <v>104</v>
@@ -510,13 +1166,16 @@
       <c r="D8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>105</v>
@@ -524,13 +1183,16 @@
       <c r="D9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <v>106</v>
@@ -538,13 +1200,16 @@
       <c r="D10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1">
         <v>107</v>
@@ -552,13 +1217,16 @@
       <c r="D11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1">
         <v>108</v>
@@ -566,13 +1234,16 @@
       <c r="D12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1">
         <v>204</v>
@@ -580,13 +1251,16 @@
       <c r="D13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1">
         <v>205</v>
@@ -594,13 +1268,16 @@
       <c r="D14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1">
         <v>206</v>
@@ -608,9 +1285,12 @@
       <c r="D15" s="1">
         <v>0</v>
       </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>DishID</t>
   </si>
@@ -62,31 +62,58 @@
     <t>牛肉</t>
   </si>
   <si>
+    <t>Icons/meat_icon</t>
+  </si>
+  <si>
     <t>卷心菜</t>
   </si>
   <si>
+    <t>Icons/cabage_icon</t>
+  </si>
+  <si>
     <t>鸡腿</t>
   </si>
   <si>
+    <t>Icons/chicken_icon</t>
+  </si>
+  <si>
     <t>土豆</t>
   </si>
   <si>
+    <t>Icons/potato_icon</t>
+  </si>
+  <si>
+    <t>Icons/tomato_icon</t>
+  </si>
+  <si>
     <t>鱼</t>
   </si>
   <si>
+    <t>Icons/fish_icon</t>
+  </si>
+  <si>
     <t>烤鱼</t>
   </si>
   <si>
+    <t>Icons/fishdish_icon</t>
+  </si>
+  <si>
     <t>13001;2|14001;5</t>
   </si>
   <si>
     <t>土豆咖喱牛腩</t>
   </si>
   <si>
+    <t>Icons/beafsoup_icon</t>
+  </si>
+  <si>
     <t>13001;0.5|14001;5</t>
   </si>
   <si>
     <t>葱鸡腿</t>
+  </si>
+  <si>
+    <t>Icons/Onionchicken_icon</t>
   </si>
   <si>
     <t>13001;1|14001;5</t>
@@ -1030,7 +1057,8 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="8.66666666666667" style="1"/>
+    <col min="1" max="3" width="8.66666666666667" style="1"/>
+    <col min="4" max="4" width="44.6666666666667" style="1" customWidth="1"/>
     <col min="5" max="5" width="37.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1146,8 +1174,8 @@
       <c r="C7" s="1">
         <v>103</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1158,13 +1186,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>104</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1175,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
         <v>105</v>
       </c>
-      <c r="D9" s="1">
-        <v>0</v>
+      <c r="D9" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1192,13 +1220,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1">
         <v>106</v>
       </c>
-      <c r="D10" s="1">
-        <v>0</v>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1214,8 +1242,8 @@
       <c r="C11" s="1">
         <v>107</v>
       </c>
-      <c r="D11" s="1">
-        <v>0</v>
+      <c r="D11" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1226,13 +1254,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1">
         <v>108</v>
       </c>
-      <c r="D12" s="1">
-        <v>0</v>
+      <c r="D12" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1243,16 +1271,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1">
         <v>204</v>
       </c>
-      <c r="D13" s="1">
-        <v>0</v>
+      <c r="D13" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1260,16 +1288,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1">
         <v>205</v>
       </c>
-      <c r="D14" s="1">
-        <v>0</v>
+      <c r="D14" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1277,16 +1305,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1">
         <v>206</v>
       </c>
-      <c r="D15" s="1">
-        <v>0</v>
+      <c r="D15" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EDADB5-6E95-463B-86D2-32633EBC138A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2DEFF4-1CD6-4E27-8A58-0EECCAB63EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6230" yWindow="350" windowWidth="14400" windowHeight="8180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18360" yWindow="3345" windowWidth="15915" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>DishID</t>
   </si>
@@ -34,18 +39,6 @@
     <t>番茄</t>
   </si>
   <si>
-    <t>鸡蛋</t>
-  </si>
-  <si>
-    <t>炒番茄</t>
-  </si>
-  <si>
-    <t>炒鸡蛋</t>
-  </si>
-  <si>
-    <t>番茄炒蛋</t>
-  </si>
-  <si>
     <t>烤鱼</t>
   </si>
   <si>
@@ -98,13 +91,21 @@
   </si>
   <si>
     <t>Assets/Sprites/Icons/Onionchicken_icon.png</t>
+  </si>
+  <si>
+    <t>CookTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>废菜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +116,15 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -139,9 +149,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -419,220 +432,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.625" style="1"/>
+    <col min="2" max="2" width="17.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="18.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1">
+        <v>103</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1">
+        <v>104</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>105</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1">
-        <v>101</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1">
-        <v>102</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>201</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C5" s="1">
-        <v>202</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>203</v>
+        <v>3</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="1">
-        <v>103</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>108</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>204</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>205</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="1">
-        <v>104</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1">
-        <v>105</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C10" s="1">
-        <v>106</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>206</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C11" s="1">
-        <v>107</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="1">
-        <v>108</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="1">
-        <v>204</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="1">
-        <v>205</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="1">
-        <v>206</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>203</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EE2BBC-198E-498C-AA1E-12E6490A1952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FBA159-AF7E-4ECE-976E-2D48027DA658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>DishID</t>
   </si>
@@ -52,18 +52,6 @@
   </si>
   <si>
     <t>番茄</t>
-  </si>
-  <si>
-    <t>鸡蛋</t>
-  </si>
-  <si>
-    <t>炒番茄</t>
-  </si>
-  <si>
-    <t>炒鸡蛋</t>
-  </si>
-  <si>
-    <t>番茄炒蛋</t>
   </si>
   <si>
     <t>牛肉</t>
@@ -465,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="8.625" style="1"/>
@@ -483,7 +471,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -497,19 +485,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
       </c>
       <c r="D2" s="1">
-        <v>101</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
+        <v>103</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -517,19 +505,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
       </c>
       <c r="D3" s="1">
-        <v>102</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
+        <v>104</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -537,19 +525,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>201</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -557,19 +545,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
       </c>
       <c r="D5" s="1">
-        <v>202</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
+        <v>106</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -577,19 +565,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="C6" s="1">
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <v>203</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -597,19 +585,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -617,181 +605,81 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>105</v>
+        <v>205</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>106</v>
+        <v>206</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>107</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
-        <v>108</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="1">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1">
-        <v>204</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="1">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1">
-        <v>205</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="1">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1">
-        <v>206</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>100</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="1">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1">
         <v>203</v>
       </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FBA159-AF7E-4ECE-976E-2D48027DA658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA4F8C7-3F38-42E0-ABA1-EEFBBC4E8A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -130,13 +127,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -144,7 +141,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -454,16 +451,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="8.625" style="1"/>
+    <col min="1" max="2" width="8.59765625" style="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="8.625" style="1"/>
-    <col min="5" max="5" width="44.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.75" customWidth="1"/>
+    <col min="4" max="4" width="8.59765625" style="1"/>
+    <col min="5" max="5" width="44.59765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,7 +480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>6</v>
       </c>
@@ -503,7 +500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>7</v>
       </c>
@@ -511,7 +508,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1">
         <v>104</v>
@@ -523,7 +520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>8</v>
       </c>
@@ -531,7 +528,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1">
         <v>105</v>
@@ -543,7 +540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>9</v>
       </c>
@@ -551,7 +548,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1">
         <v>106</v>
@@ -563,7 +560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>10</v>
       </c>
@@ -571,7 +568,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>107</v>
@@ -583,7 +580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>11</v>
       </c>
@@ -603,7 +600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>12</v>
       </c>
@@ -623,7 +620,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>13</v>
       </c>
@@ -631,7 +628,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="1">
         <v>205</v>
@@ -643,7 +640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>14</v>
       </c>
@@ -651,7 +648,7 @@
         <v>23</v>
       </c>
       <c r="C10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="1">
         <v>206</v>
@@ -663,7 +660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>100</v>
       </c>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA4F8C7-3F38-42E0-ABA1-EEFBBC4E8A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A0F523-C287-44BB-9419-384ACB1315D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>DishID</t>
   </si>
@@ -116,6 +116,32 @@
   </si>
   <si>
     <t>废菜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Icons/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+      </rPr>
+      <t>Junk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_icon</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -123,7 +149,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +172,20 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -167,12 +207,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -673,8 +716,8 @@
       <c r="D11" s="1">
         <v>203</v>
       </c>
-      <c r="E11" s="1">
-        <v>0</v>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A0F523-C287-44BB-9419-384ACB1315D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0050E2-22F5-46A6-AC2D-D0F412174D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -119,29 +122,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Icons/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-      </rPr>
-      <t>Junk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>_icon</t>
-    </r>
+    <t>Icons/Junk_icon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -149,17 +130,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Yu Gothic"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -167,7 +148,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -175,16 +156,10 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -494,16 +469,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="8.59765625" style="1"/>
+    <col min="1" max="2" width="8.625" style="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="8.59765625" style="1"/>
-    <col min="5" max="5" width="44.59765625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.69921875" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="1"/>
+    <col min="5" max="5" width="44.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>6</v>
       </c>
@@ -543,7 +518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>7</v>
       </c>
@@ -563,7 +538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>8</v>
       </c>
@@ -583,7 +558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>9</v>
       </c>
@@ -603,7 +578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>10</v>
       </c>
@@ -623,7 +598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>11</v>
       </c>
@@ -643,7 +618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>12</v>
       </c>
@@ -663,7 +638,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>13</v>
       </c>
@@ -683,7 +658,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>14</v>
       </c>
@@ -703,7 +678,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>100</v>
       </c>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0050E2-22F5-46A6-AC2D-D0F412174D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DD126A-13A9-42DA-A9F7-65699D73AF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,15 +26,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>DishID</t>
   </si>
@@ -102,16 +99,10 @@
     <t>Icons/beafsoup_icon</t>
   </si>
   <si>
-    <t>13001;0.5|14001;5</t>
-  </si>
-  <si>
     <t>葱鸡腿</t>
   </si>
   <si>
     <t>Icons/Onionchicken_icon</t>
-  </si>
-  <si>
-    <t>13001;1|14001;5</t>
   </si>
   <si>
     <t>CookTime</t>
@@ -123,6 +114,22 @@
   </si>
   <si>
     <t>Icons/Junk_icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>满汉全席</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13001;0.5|14001;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13001;1|14001;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13001;2|14001;5|13002;1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -130,17 +137,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -148,7 +155,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -156,10 +163,23 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -182,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -191,6 +211,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -468,17 +495,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="8.625" style="1"/>
+    <col min="1" max="2" width="8.59765625" style="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="8.625" style="1"/>
-    <col min="5" max="5" width="44.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.75" customWidth="1"/>
+    <col min="4" max="4" width="8.59765625" style="1"/>
+    <col min="5" max="5" width="44.59765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.69921875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -494,11 +521,11 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>6</v>
       </c>
@@ -514,11 +541,11 @@
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>7</v>
       </c>
@@ -534,11 +561,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>8</v>
       </c>
@@ -554,11 +581,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>9</v>
       </c>
@@ -574,11 +601,11 @@
       <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>10</v>
       </c>
@@ -594,11 +621,11 @@
       <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>11</v>
       </c>
@@ -614,11 +641,11 @@
       <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>12</v>
       </c>
@@ -634,11 +661,11 @@
       <c r="E8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>13</v>
       </c>
@@ -654,16 +681,16 @@
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F9" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -672,29 +699,46 @@
         <v>206</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="1">
+        <v>15</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1">
+        <v>207</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
+        <v>100</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>100</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="C12" s="1">
         <v>3</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D12" s="1">
         <v>203</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="6">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DD126A-13A9-42DA-A9F7-65699D73AF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5777EF73-3F60-44DF-8214-D64A9AB75129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>Icons/fishdish_icon</t>
   </si>
   <si>
-    <t>13001;2|14001;5</t>
-  </si>
-  <si>
     <t>土豆咖喱牛腩</t>
   </si>
   <si>
@@ -121,15 +118,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;0.5|14001;5</t>
+    <t>13001;2|14001;5|13003;10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;1|14001;5</t>
+    <t>13001;2|14001;5|13003;5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;2|14001;5|13002;1</t>
+    <t>13001;0.5|14001;5|13003;1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13001;1|14001;5|13003;1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -513,7 +514,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -662,7 +663,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -670,7 +671,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
@@ -679,10 +680,10 @@
         <v>205</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -690,7 +691,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -699,10 +700,10 @@
         <v>206</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -710,7 +711,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1">
         <v>8</v>
@@ -719,7 +720,7 @@
         <v>207</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
@@ -727,7 +728,7 @@
         <v>100</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
@@ -736,7 +737,7 @@
         <v>203</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="6">
         <v>0</v>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5777EF73-3F60-44DF-8214-D64A9AB75129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA1EAB8-031D-4C56-8BB2-8BB98FA22D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,19 +118,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;2|14001;5|13003;10</t>
+    <t>13001;2|14001;5|13003;30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;2|14001;5|13003;5</t>
+    <t>13001;2|14001;5|13003;20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;0.5|14001;5|13003;1</t>
+    <t>13001;0.5|14001;5|13003;5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;1|14001;5|13003;1</t>
+    <t>13001;1|14001;5|13003;5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA1EAB8-031D-4C56-8BB2-8BB98FA22D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F303BE4-DBB4-429B-8FF1-BDDAA06D6A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,19 +118,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;2|14001;5|13003;30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13001;2|14001;5|13003;20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>13001;0.5|14001;5|13003;5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;1|14001;5|13003;5</t>
+    <t>13001;2|14001;5|13004;10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13001;1|14001;5|13004;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13001;2|14001;5|13003;30|13004;30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -683,7 +683,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -703,7 +703,7 @@
         <v>22</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -720,7 +720,7 @@
         <v>207</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">

--- a/Assets/Configs/Dishs.xlsx
+++ b/Assets/Configs/Dishs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F303BE4-DBB4-429B-8FF1-BDDAA06D6A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008C3E89-7893-4E13-B072-C2F10BB480BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,19 +118,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;0.5|14001;5|13003;5</t>
+    <t>13001;0.5|14001;5|13003;3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;2|14001;5|13004;10</t>
+    <t>13001;1|14001;5|13004;3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;1|14001;5|13004;5</t>
+    <t>13001;2|14001;5|13003;10|13004;10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13001;2|14001;5|13003;30|13004;30</t>
+    <t>13001;2|14001;5|13004;7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -663,7 +663,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -703,7 +703,7 @@
         <v>22</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -720,7 +720,7 @@
         <v>207</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
